--- a/data/trans_dic/P55$pareja-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,59; 69,02</t>
+          <t>38,27; 68,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,13; 70,85</t>
+          <t>38,81; 69,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,0; 80,94</t>
+          <t>45,55; 80,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39,25; 62,29</t>
+          <t>40,77; 61,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 36,65</t>
+          <t>15,59; 36,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 41,62</t>
+          <t>17,8; 40,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 45,3</t>
+          <t>23,66; 44,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,39; 32,4</t>
+          <t>17,32; 32,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,99; 44,46</t>
+          <t>27,45; 45,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,53; 49,84</t>
+          <t>29,99; 49,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,06; 51,36</t>
+          <t>32,77; 52,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,81; 42,2</t>
+          <t>29,01; 42,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,21; 56,93</t>
+          <t>36,86; 57,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,79; 43,29</t>
+          <t>23,14; 43,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,34; 46,39</t>
+          <t>27,95; 45,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,78; 36,52</t>
+          <t>21,96; 36,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,14</t>
+          <t>2,11; 9,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,13</t>
+          <t>7,21; 15,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,29</t>
+          <t>5,49; 16,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,18</t>
+          <t>6,56; 11,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 24,47</t>
+          <t>14,57; 24,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 22,85</t>
+          <t>13,57; 22,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 23,84</t>
+          <t>14,61; 24,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 17,56</t>
+          <t>12,24; 17,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,84; 57,07</t>
+          <t>39,28; 58,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,49; 47,87</t>
+          <t>30,9; 49,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,67; 53,09</t>
+          <t>36,68; 53,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,3; 42,24</t>
+          <t>31,0; 42,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,03</t>
+          <t>7,31; 15,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 21,24</t>
+          <t>11,36; 20,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 23,35</t>
+          <t>12,79; 22,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,55</t>
+          <t>10,18; 15,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 29,16</t>
+          <t>19,94; 28,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,21; 27,91</t>
+          <t>19,4; 28,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,33</t>
+          <t>20,94; 30,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 22,56</t>
+          <t>17,56; 23,16</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43555</t>
+          <t>48195</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16125; 28839</t>
+          <t>15992; 28477</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17787; 32208</t>
+          <t>17643; 31744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14729; 25366</t>
+          <t>14274; 25174</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19788; 31407</t>
+          <t>22447; 34083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10924; 24794</t>
+          <t>10551; 24361</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13166; 29019</t>
+          <t>12410; 28011</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19091; 37210</t>
+          <t>19436; 36921</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13429; 23663</t>
+          <t>13944; 25768</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29540; 48661</t>
+          <t>30043; 49273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35160; 57408</t>
+          <t>34537; 57239</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37520; 58278</t>
+          <t>37188; 59475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35565; 52098</t>
+          <t>39328; 57036</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>57746</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30708; 48276</t>
+          <t>31253; 48368</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22952; 43601</t>
+          <t>23307; 44197</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24638; 41804</t>
+          <t>25186; 41230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24297; 38952</t>
+          <t>25042; 41220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3474; 14927</t>
+          <t>3444; 15338</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14337; 33835</t>
+          <t>15132; 32837</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10464; 30173</t>
+          <t>10175; 30287</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16270; 28523</t>
+          <t>18160; 32358</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36067; 60709</t>
+          <t>36151; 60982</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41906; 70955</t>
+          <t>42140; 70514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40413; 65632</t>
+          <t>40237; 66627</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42870; 63558</t>
+          <t>47850; 68995</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>105940</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51690; 72241</t>
+          <t>49719; 73993</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44567; 69964</t>
+          <t>45161; 71663</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43323; 64488</t>
+          <t>44557; 64999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46020; 66350</t>
+          <t>52421; 72556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16649; 34700</t>
+          <t>16892; 35436</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31763; 59367</t>
+          <t>31767; 56176</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33670; 62436</t>
+          <t>34196; 60696</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31765; 47763</t>
+          <t>36380; 54257</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70432; 104258</t>
+          <t>71300; 103352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81765; 118811</t>
+          <t>82601; 119601</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82445; 117938</t>
+          <t>81430; 119400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84524; 109498</t>
+          <t>92447; 121905</t>
         </is>
       </c>
     </row>
